--- a/importaciones_productos/FA265489 registro productos.xlsx
+++ b/importaciones_productos/FA265489 registro productos.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PROGLIGRg</t>
+          <t>PROGLIX20g</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CAOUSPg</t>
+          <t>GLIUSPg</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CAOLIN USP</t>
+          <t>GLICERINA USP GR X 25KG</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5.83</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -635,12 +635,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ACISALCHIg</t>
+          <t>CAOUSPg</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ACIDO SALICILICO CHINO USP</t>
+          <t>CAOLIN USP</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>25.92</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="7">
@@ -668,12 +668,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ALCCETESTg</t>
+          <t>ACISALCHIg</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ALCOHOL CETO ESTEARILICO=LANET</t>
+          <t>ACIDO SALICILICO CHINO USP</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>21.71</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="8">
@@ -701,12 +701,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CERABEBLAg</t>
+          <t>ALCCETESTg</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CERA DE ABEJAS BLANCA NACION</t>
+          <t>ALCOHOL CETO ESTEARILICO=LANET</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>21.66</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="9">
@@ -734,12 +734,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>CERABEAMAg</t>
+          <t>DEXMONg</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>CERA DE ABEJAS AMARILLA NACION</t>
+          <t>DEXTROSA MONOHIDRATADA</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>21.66</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="10">
@@ -767,12 +767,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>INULINg</t>
+          <t>CERABEBLAg</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INULINA/LINULINA</t>
+          <t>CERA DE ABEJAS BLANCA NACION</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>32.96</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="11">
@@ -800,12 +800,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>COCDEAGRg</t>
+          <t>CERABEAMAg</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>COCOAMIDA DEA GR X 20 KG</t>
+          <t>CERA DE ABEJAS AMARILLA NACION</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>16.42</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="12">
@@ -833,12 +833,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>GLIUSPGRg</t>
+          <t>INULINg</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>GLICERINA USP GR X 25KG</t>
+          <t>INULINA/LINULINA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="13">
@@ -866,12 +866,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>DEXMONg</t>
+          <t>ACERICGRFg</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>DEXTROSA MONOHIDRATADA</t>
+          <t>ACEITE DE RICINO GRF X 20 KG</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>5.47</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="14">
@@ -899,12 +899,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ACERICGRFg</t>
+          <t>COCDEAg</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ACEITE DE RICINO GRF X 20 KG</t>
+          <t>COCOAMIDA DEA GR X 20 KG</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20.23</v>
+        <v>16.42</v>
       </c>
     </row>
   </sheetData>
